--- a/quizzes/013_ugo_foscolo_knowledge_quiz--quizzes.xlsx
+++ b/quizzes/013_ugo_foscolo_knowledge_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option1':_'how_do_you_feel_about_the_story?',_'options':_['1._it_is_a_great_story',_'2._not_very_good',_"3._it's_okay"]}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option1': 'How do you feel about the story?', 'options': ['1. It is a great story', '2. Not very good', "3. It's okay"]}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option2':_'what_do_you_think_about_the_main_character?',_'options':_['1._the_main_character_is_very_smart',_'2._not_very_smart',_'3._average']}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option2': 'What do you think about the main character?', 'options': ['1. The main character is very smart', '2. Not very smart', '3. Average']}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option1':_'option_1',_'options':_['sub-option_1',_'sub-option_2',_'sub-option_3']}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option1': 'Option 1', 'options': ['Sub-option 1', 'Sub-option 2', 'Sub-option 3']}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option2':_'option_2',_'options':_['sub-option_1',_'sub-option_2',_'sub-option_3']}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option2': 'Option 2', 'options': ['Sub-option 1', 'Sub-option 2', 'Sub-option 3']}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option1':_'option_1',_'options':_['sub-option_1',_'sub-option_2']}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option1': 'Option 1', 'options': ['Sub-option 1', 'Sub-option 2']}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option2':_'option_2',_'options':_['sub-option_1',_'sub-option_2']}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option2': 'Option 2', 'options': ['Sub-option 1', 'Sub-option 2']}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option1':_'option_1',_'options':_['sub-option_1',_'sub-option_2']}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option1': 'Option 1', 'options': ['Sub-option 1', 'Sub-option 2']}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option2':_'option_2',_'options':_['sub-option_1',_'sub-option_2']}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option2': 'Option 2', 'options': ['Sub-option 1', 'Sub-option 2']}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
